--- a/forms/trg/Formulir_TRG_mgsd.xlsx
+++ b/forms/trg/Formulir_TRG_mgsd.xlsx
@@ -771,7 +771,7 @@
         </is>
       </c>
       <c r="B24" s="7">
-        <f>COUNTA(Anggota!B5:B26)</f>
+        <f>COUNTA(Anggota!B5:B27)</f>
         <v/>
       </c>
     </row>
@@ -782,7 +782,7 @@
         </is>
       </c>
       <c r="B25" s="7">
-        <f>COUNTA(Anggota!F5:F26)</f>
+        <f>COUNTA(Anggota!F5:F27)</f>
         <v/>
       </c>
     </row>
@@ -808,7 +808,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M26"/>
+  <dimension ref="A1:M27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -913,19 +913,15 @@
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
-          <t>Nuralamsyah Ismail, S.Sos., M.A.</t>
+          <t>Prof. Dr. Alwi, M.Si</t>
         </is>
       </c>
       <c r="C5" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
-        </is>
-      </c>
-      <c r="D5" s="11" t="inlineStr">
-        <is>
-          <t>Hasanuddin University</t>
-        </is>
-      </c>
+          <t>Leader</t>
+        </is>
+      </c>
+      <c r="D5" s="12" t="n"/>
       <c r="E5" s="11" t="inlineStr">
         <is>
           <t>Public Policy</t>
@@ -937,13 +933,17 @@
       <c r="I5" s="12" t="n"/>
       <c r="J5" s="11" t="inlineStr">
         <is>
-          <t>0009-0006-8341-6571</t>
-        </is>
-      </c>
-      <c r="K5" s="12" t="n"/>
+          <t>0000-0001-7785-8548</t>
+        </is>
+      </c>
+      <c r="K5" s="11" t="inlineStr">
+        <is>
+          <t>6021519</t>
+        </is>
+      </c>
       <c r="L5" s="11" t="inlineStr">
         <is>
-          <t>59073945500</t>
+          <t>57205055342</t>
         </is>
       </c>
       <c r="M5" s="11" t="inlineStr">
@@ -958,31 +958,39 @@
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>Irma Ariyanti, S.Sos., M.Si</t>
+          <t>Nuralamsyah Ismail, S.Sos., M.A.</t>
         </is>
       </c>
       <c r="C6" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
-        </is>
-      </c>
-      <c r="D6" s="12" t="n"/>
+          <t>Lecturer</t>
+        </is>
+      </c>
+      <c r="D6" s="11" t="inlineStr">
+        <is>
+          <t>Hasanuddin University</t>
+        </is>
+      </c>
       <c r="E6" s="11" t="inlineStr">
         <is>
-          <t>Public Organization</t>
+          <t>Public Policy</t>
         </is>
       </c>
       <c r="F6" s="12" t="n"/>
       <c r="G6" s="12" t="n"/>
       <c r="H6" s="12" t="n"/>
       <c r="I6" s="12" t="n"/>
-      <c r="J6" s="12" t="n"/>
-      <c r="K6" s="11" t="inlineStr">
-        <is>
-          <t>6781101</t>
-        </is>
-      </c>
-      <c r="L6" s="12" t="n"/>
+      <c r="J6" s="11" t="inlineStr">
+        <is>
+          <t>0009-0006-8341-6571</t>
+        </is>
+      </c>
+      <c r="K6" s="12" t="n"/>
+      <c r="L6" s="11" t="inlineStr">
+        <is>
+          <t>59073945500</t>
+        </is>
+      </c>
       <c r="M6" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -995,22 +1003,18 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>Dr. Ishak Salim, S.IP., M.A</t>
+          <t>Irma Ariyanti, S.Sos., M.Si</t>
         </is>
       </c>
       <c r="C7" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
-        </is>
-      </c>
-      <c r="D7" s="11" t="inlineStr">
-        <is>
-          <t>Hasanuddin University</t>
-        </is>
-      </c>
+          <t>Lecturer</t>
+        </is>
+      </c>
+      <c r="D7" s="12" t="n"/>
       <c r="E7" s="11" t="inlineStr">
         <is>
-          <t>Public Policy, Disabilities Studies</t>
+          <t>Public Organization</t>
         </is>
       </c>
       <c r="F7" s="12" t="n"/>
@@ -1018,7 +1022,11 @@
       <c r="H7" s="12" t="n"/>
       <c r="I7" s="12" t="n"/>
       <c r="J7" s="12" t="n"/>
-      <c r="K7" s="12" t="n"/>
+      <c r="K7" s="11" t="inlineStr">
+        <is>
+          <t>6781101</t>
+        </is>
+      </c>
       <c r="L7" s="12" t="n"/>
       <c r="M7" s="11" t="inlineStr">
         <is>
@@ -1032,12 +1040,12 @@
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>Andi Ahmad Yani, S.Sos, M.Si, MPA, M.Sc</t>
+          <t>Dr. Ishak Salim, S.IP., M.A</t>
         </is>
       </c>
       <c r="C8" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D8" s="11" t="inlineStr">
@@ -1047,28 +1055,16 @@
       </c>
       <c r="E8" s="11" t="inlineStr">
         <is>
-          <t>Governance and Public Policy</t>
+          <t>Public Policy, Disabilities Studies</t>
         </is>
       </c>
       <c r="F8" s="12" t="n"/>
       <c r="G8" s="12" t="n"/>
       <c r="H8" s="12" t="n"/>
       <c r="I8" s="12" t="n"/>
-      <c r="J8" s="11" t="inlineStr">
-        <is>
-          <t>0000-0003-3401-7639</t>
-        </is>
-      </c>
-      <c r="K8" s="11" t="inlineStr">
-        <is>
-          <t>22338</t>
-        </is>
-      </c>
-      <c r="L8" s="11" t="inlineStr">
-        <is>
-          <t>57204899767</t>
-        </is>
-      </c>
+      <c r="J8" s="12" t="n"/>
+      <c r="K8" s="12" t="n"/>
+      <c r="L8" s="12" t="n"/>
       <c r="M8" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -1081,12 +1077,12 @@
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>Prof. Dr. Gita Susanti, M.Si</t>
+          <t>Andi Ahmad Yani, S.Sos, M.Si, MPA, M.Sc</t>
         </is>
       </c>
       <c r="C9" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D9" s="11" t="inlineStr">
@@ -1096,22 +1092,26 @@
       </c>
       <c r="E9" s="11" t="inlineStr">
         <is>
-          <t>Adaptive Capacity</t>
+          <t>Governance and Public Policy</t>
         </is>
       </c>
       <c r="F9" s="12" t="n"/>
       <c r="G9" s="12" t="n"/>
       <c r="H9" s="12" t="n"/>
       <c r="I9" s="12" t="n"/>
-      <c r="J9" s="12" t="n"/>
+      <c r="J9" s="11" t="inlineStr">
+        <is>
+          <t>0000-0003-3401-7639</t>
+        </is>
+      </c>
       <c r="K9" s="11" t="inlineStr">
         <is>
-          <t>6028100</t>
+          <t>22338</t>
         </is>
       </c>
       <c r="L9" s="11" t="inlineStr">
         <is>
-          <t>57960322800</t>
+          <t>57204899767</t>
         </is>
       </c>
       <c r="M9" s="11" t="inlineStr">
@@ -1126,22 +1126,22 @@
       </c>
       <c r="B10" s="11" t="inlineStr">
         <is>
-          <t>Prof. Madya Dr. Nor Hafizah Binti Mohamed Harith</t>
+          <t>Prof. Dr. Gita Susanti, M.Si</t>
         </is>
       </c>
       <c r="C10" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D10" s="11" t="inlineStr">
         <is>
-          <t>Universiti Teknologi MARA (UiTM)</t>
+          <t>Hasanuddin University</t>
         </is>
       </c>
       <c r="E10" s="11" t="inlineStr">
         <is>
-          <t>Public Policy</t>
+          <t>Adaptive Capacity</t>
         </is>
       </c>
       <c r="F10" s="12" t="n"/>
@@ -1149,8 +1149,16 @@
       <c r="H10" s="12" t="n"/>
       <c r="I10" s="12" t="n"/>
       <c r="J10" s="12" t="n"/>
-      <c r="K10" s="12" t="n"/>
-      <c r="L10" s="12" t="n"/>
+      <c r="K10" s="11" t="inlineStr">
+        <is>
+          <t>6028100</t>
+        </is>
+      </c>
+      <c r="L10" s="11" t="inlineStr">
+        <is>
+          <t>57960322800</t>
+        </is>
+      </c>
       <c r="M10" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -1163,22 +1171,22 @@
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t>Sri Nurindah Sari Arsyad, S.Sos., M.A.P</t>
+          <t>Prof. Madya Dr. Nor Hafizah Binti Mohamed Harith</t>
         </is>
       </c>
       <c r="C11" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D11" s="11" t="inlineStr">
         <is>
-          <t>Hasanuddin University</t>
+          <t>Universiti Teknologi MARA (UiTM)</t>
         </is>
       </c>
       <c r="E11" s="11" t="inlineStr">
         <is>
-          <t>Public Organization</t>
+          <t>Public Policy</t>
         </is>
       </c>
       <c r="F11" s="12" t="n"/>
@@ -1200,12 +1208,12 @@
       </c>
       <c r="B12" s="11" t="inlineStr">
         <is>
-          <t>Regina Sapta Samudera, S.A.P., M.A.P</t>
+          <t>Sri Nurindah Sari Arsyad, S.Sos., M.A.P</t>
         </is>
       </c>
       <c r="C12" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D12" s="11" t="inlineStr">
@@ -1215,7 +1223,7 @@
       </c>
       <c r="E12" s="11" t="inlineStr">
         <is>
-          <t>Public Policy</t>
+          <t>Public Organization</t>
         </is>
       </c>
       <c r="F12" s="12" t="n"/>
@@ -1237,16 +1245,24 @@
       </c>
       <c r="B13" s="11" t="inlineStr">
         <is>
-          <t>Nurazizah Salsadila</t>
+          <t>Regina Sapta Samudera, S.A.P., M.A.P</t>
         </is>
       </c>
       <c r="C13" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
-        </is>
-      </c>
-      <c r="D13" s="12" t="n"/>
-      <c r="E13" s="11" t="n"/>
+          <t>Researcher</t>
+        </is>
+      </c>
+      <c r="D13" s="11" t="inlineStr">
+        <is>
+          <t>Hasanuddin University</t>
+        </is>
+      </c>
+      <c r="E13" s="11" t="inlineStr">
+        <is>
+          <t>Public Policy</t>
+        </is>
+      </c>
       <c r="F13" s="12" t="n"/>
       <c r="G13" s="12" t="n"/>
       <c r="H13" s="12" t="n"/>
@@ -1266,12 +1282,12 @@
       </c>
       <c r="B14" s="11" t="inlineStr">
         <is>
-          <t>Sulfira</t>
+          <t>Nurazizah Salsadila</t>
         </is>
       </c>
       <c r="C14" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D14" s="12" t="n"/>
@@ -1293,8 +1309,16 @@
       <c r="A15" s="4" t="n">
         <v>11</v>
       </c>
-      <c r="B15" s="12" t="n"/>
-      <c r="C15" s="12" t="n"/>
+      <c r="B15" s="11" t="inlineStr">
+        <is>
+          <t>Sulfira</t>
+        </is>
+      </c>
+      <c r="C15" s="11" t="inlineStr">
+        <is>
+          <t>Student</t>
+        </is>
+      </c>
       <c r="D15" s="12" t="n"/>
       <c r="E15" s="11" t="n"/>
       <c r="F15" s="12" t="n"/>
@@ -1304,7 +1328,11 @@
       <c r="J15" s="12" t="n"/>
       <c r="K15" s="12" t="n"/>
       <c r="L15" s="12" t="n"/>
-      <c r="M15" s="12" t="n"/>
+      <c r="M15" s="11" t="inlineStr">
+        <is>
+          <t>Aktif</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="n">
@@ -1493,15 +1521,32 @@
       <c r="L26" s="12" t="n"/>
       <c r="M26" s="12" t="n"/>
     </row>
+    <row r="27">
+      <c r="A27" s="4" t="n">
+        <v>23</v>
+      </c>
+      <c r="B27" s="12" t="n"/>
+      <c r="C27" s="12" t="n"/>
+      <c r="D27" s="12" t="n"/>
+      <c r="E27" s="11" t="n"/>
+      <c r="F27" s="12" t="n"/>
+      <c r="G27" s="12" t="n"/>
+      <c r="H27" s="12" t="n"/>
+      <c r="I27" s="12" t="n"/>
+      <c r="J27" s="12" t="n"/>
+      <c r="K27" s="12" t="n"/>
+      <c r="L27" s="12" t="n"/>
+      <c r="M27" s="12" t="n"/>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A2:M2"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation sqref="F5:H26" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F5:H27" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Daftar!$A$2:$A$39</formula1>
     </dataValidation>
-    <dataValidation sqref="M5:M26" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="M5:M27" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Daftar!$C$2:$C$3</formula1>
     </dataValidation>
   </dataValidations>
